--- a/output/第10期計画_算定方法の整合確認_国と見える化.xlsx
+++ b/output/第10期計画_算定方法の整合確認_国と見える化.xlsx
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>介護老人福祉施設の定員は平成29年234人から令和2年以降160人へ31.6％縮小している。特定施設は定員156人に対し入居者154人（98.7％）でほぼ満室。自然体推計は定員を超えても止まらない。</t>
+          <t>介護老人福祉施設の定員は平成29年234人から令和2年以降160人へ31.6％縮小している。特定施設は区域内3施設とも入居率が高い（98.3％と97.0％。合計の98.7％は時点が異なる参考値）。自然体推計は定員を超えても止まらない。</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>自然体推計は定員を超えても止まりません。介護老人福祉施設の定員は31.6％縮小し、特定施設は入居率98.7％でほぼ満室です。定員による上限を掛けるかどうか。</t>
+          <t>自然体推計は定員を超えても止まりません。介護老人福祉施設の定員は31.6％縮小し、特定施設は区域内3施設とも入居率が高くなっています（98.3％と97.0％。合計の98.7％は時点が異なる参考値）。定員による上限を掛けるかどうか。</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
